--- a/Data/RebateTemplates/roberto-rmb.xlsx
+++ b/Data/RebateTemplates/roberto-rmb.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle" sheetId="1" r:id="Re1c0e326b5fb499f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monto de factura" sheetId="2" r:id="R141e8f2f37ed4ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REBAJO" sheetId="3" r:id="R656f7452980c40cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle" sheetId="1" r:id="R8fed8053114a4dd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monto de factura" sheetId="2" r:id="R3357c16a1860402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REBAJO" sheetId="3" r:id="Rf2c89d2c40a24663"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5040,7 +5040,7 @@
         <x:v>460</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>TC FIJO</x:v>
+        <x:v>TC</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
